--- a/data/archive/2026-08-30-ncaaf-synthetic-main-quarantine/ncaaf.xlsx
+++ b/data/archive/2026-08-30-ncaaf-synthetic-main-quarantine/ncaaf.xlsx
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="L2" s="26" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="M2" s="27" t="n">
-        <v>2</v>
+        <v>1.909091</v>
       </c>
       <c r="N2" s="28" t="n">
-        <v>0.5</v>
+        <v>0.52381</v>
       </c>
       <c r="O2" s="28" t="n">
         <v>0.875533</v>
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="M4" s="27" t="n">
-        <v>2</v>
+        <v>1.909091</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.5</v>
+        <v>0.52381</v>
       </c>
       <c r="O4" s="28" t="n">
         <v>0.584467</v>
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>2</v>
+        <v>1.909091</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.5</v>
+        <v>0.52381</v>
       </c>
       <c r="O5" s="28" t="n">
         <v>0.749867</v>
@@ -3069,13 +3069,13 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>2</v>
+        <v>1.909091</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.5</v>
+        <v>0.52381</v>
       </c>
       <c r="O6" s="28" t="n">
         <v>0.882333</v>
@@ -3385,13 +3385,13 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2</v>
+        <v>1.909091</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.5</v>
+        <v>0.52381</v>
       </c>
       <c r="O7" s="28" t="n">
         <v>0.724867</v>
@@ -3701,13 +3701,13 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>2</v>
+        <v>1.909091</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.5</v>
+        <v>0.52381</v>
       </c>
       <c r="O8" s="28" t="n">
         <v>0.858067</v>
@@ -3750,7 +3750,7 @@
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
       <c r="AC8" s="30" t="n">
-        <v>2</v>
+        <v>1.8182</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
         <is>
@@ -4017,13 +4017,13 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>2</v>
+        <v>1.909091</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.5</v>
+        <v>0.52381</v>
       </c>
       <c r="O9" s="28" t="n">
         <v>0.6126</v>
